--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.1</t>
+          <t>00:010.2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.1</t>
+          <t>00:017.3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>233.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>413.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>14.39</t>
+          <t>97.19</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>715344</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -583,44 +583,44 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:026.9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>966.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>513.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30053</t>
+          <t>1774598</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.1</t>
+          <t>00:035.8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>1073.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>669.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>2158606</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,47 +704,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.9</t>
+          <t>00:052.5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>290.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>333.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63887</t>
+          <t>2232215</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.9</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>226.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>106.7</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65907</t>
+          <t>2310687</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,34 +811,34 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.1</t>
+          <t>01:009.1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>487.4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>493.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>20.39</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>2476419</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,34 +868,34 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.9</t>
+          <t>01:020.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>546.2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>490.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70415</t>
+          <t>2663382</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.3</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>33.4</t>
+          <t>266.5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>69864</t>
+          <t>2757348</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:039.9</t>
+          <t>01:040.3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>181.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.88</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>2813335</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1039,34 +1039,34 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>237.4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12.44</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>84602</t>
+          <t>2896242</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:000.0</t>
+          <t>01:059.8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>300.9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>140.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.60</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>95450</t>
+          <t>3007862</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:009.7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>259.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>135.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>96034</t>
+          <t>3091454</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1210,34 +1210,34 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.7</t>
+          <t>02:020.3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>205.9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>120959</t>
+          <t>3150771</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:030.2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>207.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>104.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.16</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>193500</t>
+          <t>3214549</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.6</t>
+          <t>02:035.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>94.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>235385</t>
+          <t>3246482</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1382,177 +1382,6 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>DDoS Burst</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02:050.0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>22.1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>219155</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>02:055.6</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>23.3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>21.4</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>210460</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.4</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>22.4</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>210246</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
         </is>
       </c>
     </row>

--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,12 +476,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:010.2</t>
+          <t>00:010.1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,22 +538,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>233.2</t>
+          <t>216.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>413.9</t>
+          <t>410.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>97.19</t>
+          <t>101.16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>715344</t>
+          <t>633779</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:026.9</t>
+          <t>00:029.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>966.8</t>
+          <t>895.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>513.5</t>
+          <t>512.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1774598</t>
+          <t>2016592</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:035.8</t>
+          <t>00:036.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1073.0</t>
+          <t>959.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>669.4</t>
+          <t>490.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2158606</t>
+          <t>2836320</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,37 +704,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:052.5</t>
+          <t>00:052.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>290.3</t>
+          <t>708.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>333.0</t>
+          <t>599.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2232215</t>
+          <t>3114596</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.0</t>
+          <t>01:005.3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>226.1</t>
+          <t>489.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>106.7</t>
+          <t>430.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2310687</t>
+          <t>3936395</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:009.1</t>
+          <t>01:012.4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>487.4</t>
+          <t>317.7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>493.6</t>
+          <t>266.3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20.39</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2476419</t>
+          <t>5132069</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:020.9</t>
+          <t>01:019.9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>546.2</t>
+          <t>308.7</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>490.0</t>
+          <t>262.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2663382</t>
+          <t>6386897</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.1</t>
+          <t>01:031.9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>266.5</t>
+          <t>286.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>250.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2757348</t>
+          <t>7612586</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.3</t>
+          <t>01:037.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>181.3</t>
+          <t>302.9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>256.1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,17 +1019,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2813335</t>
+          <t>8755207</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.3</t>
+          <t>01:050.9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>237.4</t>
+          <t>341.1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>331.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2896242</t>
+          <t>9678281</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.8</t>
+          <t>02:000.7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>300.9</t>
+          <t>172.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>140.6</t>
+          <t>198.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3007862</t>
+          <t>10169750</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:009.7</t>
+          <t>02:009.5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>259.0</t>
+          <t>156.9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>135.8</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3091454</t>
+          <t>10559309</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.3</t>
+          <t>02:020.8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>205.9</t>
+          <t>154.8</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>92.1</t>
+          <t>157.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3150771</t>
+          <t>10908437</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.2</t>
+          <t>02:029.5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>207.2</t>
+          <t>153.3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>104.3</t>
+          <t>189.4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3214549</t>
+          <t>11235358</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:035.1</t>
+          <t>02:041.1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>197.5</t>
+          <t>114.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>94.6</t>
+          <t>189.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3246482</t>
+          <t>11438799</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1382,6 +1382,177 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>DDoS Burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>02:049.9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>41.8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>31.2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>11418351</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02:055.1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>38.9</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11402663</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>39.9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11402098</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
